--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486704_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486704_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4167</v>
+        <v>7.1865</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3335</v>
+        <v>5.0785</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0832</v>
+        <v>2.108</v>
       </c>
       <c r="G2" t="n">
         <v>5.457</v>
@@ -610,13 +610,13 @@
         <v>0.3862</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3611</v>
+        <v>2.1309</v>
       </c>
       <c r="T2" t="n">
-        <v>1.7925</v>
+        <v>1.5374</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5686</v>
+        <v>0.5934</v>
       </c>
       <c r="V2" t="n">
         <v>0.3709</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. SOLA IDRISU</t>
+          <t>P. ROBLES LLANOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3198</v>
+        <v>5.1637</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2397</v>
+        <v>4.1234</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0801</v>
+        <v>1.0403</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7832</v>
+        <v>4.2567</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8346</v>
+        <v>2.0547</v>
       </c>
       <c r="I3" t="n">
-        <v>5.6178</v>
+        <v>2.202</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1156</v>
+        <v>3.9753</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0629</v>
+        <v>2.7454</v>
       </c>
       <c r="L3" t="n">
-        <v>5.0527</v>
+        <v>1.2299</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3324</v>
+        <v>0.2813</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.8975</v>
+        <v>-0.6907</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5651</v>
+        <v>0.972</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1931</v>
+        <v>-3.2823</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1585</v>
+        <v>-4.0546</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3515</v>
+        <v>0.7723</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1431</v>
+        <v>0.8345</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7174</v>
+        <v>0.8478</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5742</v>
+        <v>-0.0133</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.5133</v>
+        <v>3.3548</v>
       </c>
       <c r="W3" t="n">
+        <v>3.3548</v>
+      </c>
+      <c r="X3" t="n">
         <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-1.5133</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. ROBLES LLANOS</t>
+          <t>M. SOLA IDRISU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1432</v>
+        <v>4.725</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7237</v>
+        <v>4.6946</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4195</v>
+        <v>0.0305</v>
       </c>
       <c r="G4" t="n">
-        <v>4.2567</v>
+        <v>4.7832</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0547</v>
+        <v>-0.8346</v>
       </c>
       <c r="I4" t="n">
-        <v>2.202</v>
+        <v>5.6178</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9753</v>
+        <v>5.1156</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7454</v>
+        <v>0.0629</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2299</v>
+        <v>5.0527</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2813</v>
+        <v>-0.3324</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6907</v>
+        <v>-0.8975</v>
       </c>
       <c r="O4" t="n">
-        <v>0.972</v>
+        <v>0.5651</v>
       </c>
       <c r="P4" t="n">
-        <v>-3.2823</v>
+        <v>0.1931</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4.0546</v>
+        <v>-1.1585</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7723</v>
+        <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1859</v>
+        <v>1.2621</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5518</v>
+        <v>0.7375</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6341</v>
+        <v>0.5246</v>
       </c>
       <c r="V4" t="n">
-        <v>3.3548</v>
+        <v>-1.5133</v>
       </c>
       <c r="W4" t="n">
-        <v>3.3548</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. DIAZ MARTINEZ</t>
+          <t>V. NEGRE FABREGAT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2726</v>
+        <v>1.7948</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3868</v>
+        <v>2.2742</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8859</v>
+        <v>-0.4794</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1182</v>
+        <v>0.239</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0829</v>
+        <v>0.248</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2012</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3818</v>
+        <v>1.4537</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7457</v>
+        <v>0.3865</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.3639</v>
+        <v>1.0671</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2635</v>
+        <v>-1.2146</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8286</v>
+        <v>-0.1385</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5651</v>
+        <v>-1.0761</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>3.0618</v>
+        <v>-0.7378</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2061</v>
+        <v>-0.4071</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8557</v>
+        <v>-0.3307</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3282</v>
+        <v>0.9421</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0426</v>
+        <v>1.2277</v>
       </c>
       <c r="X5" t="n">
         <v>-0.2856</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>F. DIAZ MARTINEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8519</v>
+        <v>1.3555</v>
       </c>
       <c r="E6" t="n">
-        <v>2.3794</v>
+        <v>0.718</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5275</v>
+        <v>0.6375</v>
       </c>
       <c r="G6" t="n">
-        <v>1.8935</v>
+        <v>0.1182</v>
       </c>
       <c r="H6" t="n">
-        <v>1.586</v>
+        <v>-0.0829</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3074</v>
+        <v>0.2012</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1287</v>
+        <v>0.3818</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9659</v>
+        <v>0.7457</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1628</v>
+        <v>-0.3639</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7648</v>
+        <v>-0.2635</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6201</v>
+        <v>-0.8286</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1447</v>
+        <v>0.5651</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1931</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1931</v>
+        <v>-1.1585</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="S6" t="n">
-        <v>0.993</v>
+        <v>2.1447</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1582</v>
+        <v>1.5373</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1652</v>
+        <v>0.6074000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2277</v>
+        <v>-0.3282</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2856</v>
+        <v>-0.0426</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.5133</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. NEGRE FABREGAT</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.33</v>
+        <v>1.2314</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9088</v>
+        <v>1.7589</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5788</v>
+        <v>-0.5275</v>
       </c>
       <c r="G7" t="n">
-        <v>0.239</v>
+        <v>1.8935</v>
       </c>
       <c r="H7" t="n">
-        <v>0.248</v>
+        <v>1.586</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.008999999999999999</v>
+        <v>0.3074</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4537</v>
+        <v>1.1287</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3865</v>
+        <v>0.9659</v>
       </c>
       <c r="L7" t="n">
-        <v>1.0671</v>
+        <v>0.1628</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2146</v>
+        <v>0.7648</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1385</v>
+        <v>0.6201</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0761</v>
+        <v>0.1447</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3515</v>
+        <v>0.1931</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2026</v>
+        <v>0.3725</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7725</v>
+        <v>0.5377</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4301</v>
+        <v>-0.1652</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9421</v>
+        <v>-1.2277</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2277</v>
+        <v>0.2856</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2856</v>
+        <v>-1.5133</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4069</v>
+        <v>-0.9887</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6051</v>
+        <v>0.6812</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1982</v>
+        <v>-1.67</v>
       </c>
       <c r="G8" t="n">
         <v>-1.0218</v>
@@ -1078,13 +1078,13 @@
         <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6645</v>
+        <v>1.2688</v>
       </c>
       <c r="T8" t="n">
-        <v>1.875</v>
+        <v>0.9510999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7895</v>
+        <v>0.3177</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6565</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5693</v>
+        <v>-1.1045</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2025</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.7718</v>
+        <v>-1.6725</v>
       </c>
       <c r="G9" t="n">
         <v>0.643</v>
@@ -1156,13 +1156,13 @@
         <v>0.7723</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1198</v>
+        <v>-0.655</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5518</v>
+        <v>-0.1864</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.4686</v>
       </c>
       <c r="V9" t="n">
         <v>-0.8995</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.3558</v>
+        <v>-2.153</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.5182</v>
+        <v>-2.4148</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1624</v>
+        <v>0.2618</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5393</v>
@@ -1234,13 +1234,13 @@
         <v>0.5792</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4303</v>
+        <v>-0.2276</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2759</v>
+        <v>-0.1725</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1544</v>
+        <v>-0.0551</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.5581</v>
+        <v>-3.4007</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9256</v>
+        <v>-2.5943</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6325</v>
+        <v>-0.8064</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2437</v>
@@ -1312,13 +1312,13 @@
         <v>1.1585</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3806</v>
+        <v>-0.462</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6616</v>
+        <v>-0.0072</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.281</v>
+        <v>-0.4548</v>
       </c>
       <c r="V11" t="n">
         <v>0.0426</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.2579</v>
+        <v>13.81</v>
       </c>
       <c r="E12" t="n">
-        <v>14.3357</v>
+        <v>14.8877</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0777</v>
+        <v>-1.077700000000001</v>
       </c>
       <c r="G12" t="n">
         <v>13.5858</v>
@@ -1360,7 +1360,7 @@
         <v>4.825600000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>8.760299999999999</v>
+        <v>8.760300000000001</v>
       </c>
       <c r="J12" t="n">
         <v>18.5961</v>
@@ -1390,19 +1390,19 @@
         <v>8.6884</v>
       </c>
       <c r="S12" t="n">
-        <v>5.379300000000001</v>
+        <v>5.9311</v>
       </c>
       <c r="T12" t="n">
-        <v>4.824</v>
+        <v>5.3756</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5552000000000001</v>
+        <v>0.5554000000000002</v>
       </c>
       <c r="V12" t="n">
-        <v>0.08519999999999997</v>
+        <v>0.0851999999999993</v>
       </c>
       <c r="W12" t="n">
-        <v>5.3967</v>
+        <v>5.396699999999999</v>
       </c>
       <c r="X12" t="n">
         <v>-5.311500000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.8638</v>
+        <v>4.4513</v>
       </c>
       <c r="E13" t="n">
-        <v>4.2389</v>
+        <v>4.6526</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3752</v>
+        <v>-0.2013</v>
       </c>
       <c r="G13" t="n">
         <v>1.5381</v>
@@ -1468,13 +1468,13 @@
         <v>2.51</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1531</v>
+        <v>-0.5656</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2764</v>
+        <v>0.1373</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.8767</v>
+        <v>-0.7029</v>
       </c>
       <c r="V13" t="n">
         <v>2.1271</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1739</v>
+        <v>0.6361</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0325</v>
+        <v>0.6188</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1414</v>
+        <v>0.0172</v>
       </c>
       <c r="G14" t="n">
         <v>-0.5816</v>
@@ -1546,13 +1546,13 @@
         <v>0.7723</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2688</v>
+        <v>0.7309</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8823</v>
+        <v>0.4686</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3865</v>
+        <v>0.2623</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2856</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9281</v>
+        <v>-0.1834</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.734</v>
+        <v>-1.1135</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8058999999999999</v>
+        <v>0.9301</v>
       </c>
       <c r="G15" t="n">
         <v>-0.4994</v>
@@ -1624,13 +1624,13 @@
         <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7723</v>
+        <v>-0.0276</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6898</v>
+        <v>-0.0693</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0824</v>
+        <v>0.0417</v>
       </c>
       <c r="V15" t="n">
         <v>-0.0426</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.0645</v>
+        <v>-0.8038999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3724</v>
+        <v>1.6827</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.437</v>
+        <v>-2.4866</v>
       </c>
       <c r="G16" t="n">
         <v>-0.8977000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>2.1239</v>
       </c>
       <c r="S16" t="n">
-        <v>-2.0743</v>
+        <v>-1.8137</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8555</v>
+        <v>-0.5452</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.2188</v>
+        <v>-1.2684</v>
       </c>
       <c r="V16" t="n">
         <v>0.9421</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.6791</v>
+        <v>-1.2903</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.9283</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7508</v>
+        <v>-0.7756</v>
       </c>
       <c r="G17" t="n">
         <v>-2.4214</v>
@@ -1780,13 +1780,13 @@
         <v>0.5792</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0647</v>
+        <v>-0.6758</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4966</v>
+        <v>-0.083</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5679999999999999</v>
+        <v>-0.5929</v>
       </c>
       <c r="V17" t="n">
         <v>1.2277</v>
@@ -1813,10 +1813,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.9614</v>
+        <v>-2.5477</v>
       </c>
       <c r="E18" t="n">
-        <v>0.888</v>
+        <v>1.3017</v>
       </c>
       <c r="F18" t="n">
         <v>-3.8494</v>
@@ -1858,10 +1858,10 @@
         <v>1.3515</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2688</v>
+        <v>-0.8551</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8279</v>
+        <v>-0.4142</v>
       </c>
       <c r="U18" t="n">
         <v>-0.441</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. MURRAY</t>
+          <t>I. CONDES LOPEZ-CEPERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.3807</v>
+        <v>-4.0424</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.0386</v>
+        <v>-0.7932</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3422</v>
+        <v>-3.2492</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.8135</v>
+        <v>-4.2215</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.2957</v>
+        <v>-0.8621</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5178</v>
+        <v>-3.3593</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0158</v>
+        <v>-0.3376</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3294</v>
+        <v>1.0006</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3451</v>
+        <v>-1.3383</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.8292</v>
+        <v>-3.8838</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9664</v>
+        <v>-1.8628</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.8629</v>
+        <v>-2.0211</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.5446</v>
+        <v>1.7377</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.0546</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.51</v>
+        <v>1.7377</v>
       </c>
       <c r="S19" t="n">
-        <v>1.9194</v>
+        <v>-1.5586</v>
       </c>
       <c r="T19" t="n">
-        <v>2.3712</v>
+        <v>-0.4556</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4517</v>
+        <v>-1.103</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9421</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3709</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. CONDES LOPEZ-CEPERO</t>
+          <t>A. ANDRADE ROSSI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.8355</v>
+        <v>-4.2187</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5864</v>
+        <v>-1.0634</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.2492</v>
+        <v>-3.1553</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.2215</v>
+        <v>-1.4944</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.8621</v>
+        <v>-1.6413</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.3593</v>
+        <v>0.1469</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3376</v>
+        <v>-0.0731</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0006</v>
+        <v>-1.2962</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3383</v>
+        <v>1.2231</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.8838</v>
+        <v>-1.4212</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.8628</v>
+        <v>-0.3451</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.0211</v>
+        <v>-1.0761</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7377</v>
+        <v>0.3862</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7377</v>
+        <v>1.3515</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3518</v>
+        <v>-0.6552</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2487</v>
+        <v>-0.3105</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.103</v>
+        <v>-0.3447</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.4554</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.741</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. ANDRADE ROSSI</t>
+          <t>C. MURRAY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4463</v>
+        <v>-5.259</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.1668</v>
+        <v>-3.6933</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.2795</v>
+        <v>-1.5657</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4944</v>
+        <v>-2.8135</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6413</v>
+        <v>-2.2957</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1469</v>
+        <v>-0.5178</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0731</v>
+        <v>0.0158</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2962</v>
+        <v>-1.3294</v>
       </c>
       <c r="L21" t="n">
-        <v>1.2231</v>
+        <v>1.3451</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4212</v>
+        <v>-2.8292</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.3451</v>
+        <v>-0.9664</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0761</v>
+        <v>-1.8629</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3862</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9654</v>
+        <v>-4.0546</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3515</v>
+        <v>2.51</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8827</v>
+        <v>0.0412</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4139</v>
+        <v>0.7164</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4688</v>
+        <v>-0.6752</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.4554</v>
+        <v>-0.9421</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2856</v>
+        <v>-0.3709</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.741</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-13.2579</v>
+        <v>-13.258</v>
       </c>
       <c r="E22" t="n">
-        <v>1.077699999999999</v>
+        <v>1.077800000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-14.336</v>
+        <v>-14.3358</v>
       </c>
       <c r="G22" t="n">
         <v>-13.586</v>
@@ -2140,10 +2140,10 @@
         <v>-4.8255</v>
       </c>
       <c r="I22" t="n">
-        <v>-8.760300000000001</v>
+        <v>-8.760299999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>5.010199999999999</v>
+        <v>5.010199999999998</v>
       </c>
       <c r="K22" t="n">
         <v>3.8003</v>
@@ -2158,7 +2158,7 @@
         <v>-8.6259</v>
       </c>
       <c r="O22" t="n">
-        <v>-9.9701</v>
+        <v>-9.970099999999999</v>
       </c>
       <c r="P22" t="n">
         <v>5.7924</v>
@@ -2173,13 +2173,13 @@
         <v>-5.3795</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5553000000000001</v>
+        <v>-0.5555</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.8239</v>
+        <v>-4.8241</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.08530000000000015</v>
+        <v>-0.08529999999999982</v>
       </c>
       <c r="W22" t="n">
         <v>5.3114</v>
